--- a/data/ALLE_topthemen_zeitreihe.xlsx
+++ b/data/ALLE_topthemen_zeitreihe.xlsx
@@ -2592,7 +2592,7 @@
         <v>12</v>
       </c>
       <c r="C58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -4317,6 +4317,27 @@
       <c r="K107" t="n">
         <v>9</v>
       </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1"/>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4552,13 +4573,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB289F36-5F58-4D7C-A84B-8FDE997C02CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A7E6E0-7EB6-4FDA-BA71-6243DC891F32}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BE78630-9F48-4CDA-BD8B-8D202A00111C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FFD644B-CF65-495C-9936-1168FFDA2612}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FBBC2BD-D5F4-4E81-B351-E1D962B8320E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B82B68FF-A4B4-44DC-A165-1DC66D6B73D1}"/>
 </file>
--- a/data/ALLE_topthemen_zeitreihe.xlsx
+++ b/data/ALLE_topthemen_zeitreihe.xlsx
@@ -2557,7 +2557,7 @@
         <v>12</v>
       </c>
       <c r="C57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -4317,27 +4317,6 @@
       <c r="K107" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1"/>
-      <c r="B108" t="s">
-        <v>12</v>
-      </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-      <c r="I108"/>
-      <c r="J108"/>
-      <c r="K108"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4573,13 +4552,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A7E6E0-7EB6-4FDA-BA71-6243DC891F32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{696B2AA3-1754-461A-813B-8F134981427B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FFD644B-CF65-495C-9936-1168FFDA2612}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C1C177-C301-40E2-909E-FB1CCA487DF9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B82B68FF-A4B4-44DC-A165-1DC66D6B73D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F8320EB-54AA-4679-8A72-2C8C478A65DD}"/>
 </file>
--- a/data/ALLE_topthemen_zeitreihe.xlsx
+++ b/data/ALLE_topthemen_zeitreihe.xlsx
@@ -56,12 +56,12 @@
     <t xml:space="preserve">Verkehrswegebau</t>
   </si>
   <si>
+    <t xml:space="preserve">Öffentlicher Haushalt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Schadstoffe, Immissionen, Emissionen</t>
   </si>
   <si>
-    <t xml:space="preserve">Wahlen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Polizei</t>
   </si>
   <si>
@@ -83,18 +83,18 @@
     <t xml:space="preserve">Frühkindliche Bildung</t>
   </si>
   <si>
+    <t xml:space="preserve">Hochschulwesen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Luftverkehr</t>
   </si>
   <si>
-    <t xml:space="preserve">Öffentlicher Haushalt</t>
+    <t xml:space="preserve">Schulen</t>
   </si>
   <si>
     <t xml:space="preserve">Kinder, Jugendliche</t>
   </si>
   <si>
-    <t xml:space="preserve">Schulen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Klima</t>
   </si>
   <si>
@@ -128,130 +128,130 @@
     <t xml:space="preserve">Erneuerbare Energien</t>
   </si>
   <si>
+    <t xml:space="preserve">Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landwirtschaftliche Betriebe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fossile Energien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideologien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freizeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europäische Union</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allgemeinbildende Schulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katastrophen- und Zivilschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raumordnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheitsschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justizvollzug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesellschaft, Bevölkerung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordnungsrecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rundfunk, Fernsehen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wald, Forsten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bauwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentliches Vermögen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentliche Vergabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frauen, Männer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landwirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsbedingungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berufsbildende Schulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonderpädagogik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schienenverkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abgaben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzverwaltung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politische Kräfte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentlicher Dienst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschulen für angewandte Wissenschaften</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitäten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Religionsgemeinschaften</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gewerbliche Wirtschaft, Industrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Güterverkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentliche Verwaltung</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kunst, Kultur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landwirtschaftliche Betriebe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fossile Energien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideologien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Europäische Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allgemeinbildende Schulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katastrophen- und Zivilschutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochschulwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raumordnung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheitsschutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justizvollzug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesellschaft, Bevölkerung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordnungsrecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rundfunk, Fernsehen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wald, Forsten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bauwesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentliches Vermögen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentliche Vergabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frauen, Männer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landwirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitsbedingungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berufsbildende Schulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonderpädagogik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schienenverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abgaben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzverwaltung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politische Kräfte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentlicher Dienst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochschulen für angewandte Wissenschaften</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universitäten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Religionsgemeinschaften</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gewerbliche Wirtschaft, Industrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Güterverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentliche Verwaltung</t>
   </si>
   <si>
     <t xml:space="preserve">Verfassungsschutz, Spionage</t>
@@ -632,25 +632,25 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -679,13 +679,13 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -702,7 +702,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -772,31 +772,31 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -810,25 +810,25 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="s">
         <v>13</v>
-      </c>
-      <c r="I7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>23</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
@@ -839,7 +839,7 @@
         <v>43070</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
@@ -860,13 +860,13 @@
         <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -886,13 +886,13 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
         <v>16</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
@@ -901,7 +901,7 @@
         <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -915,25 +915,25 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
@@ -947,19 +947,19 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
         <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -968,7 +968,7 @@
         <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
@@ -982,22 +982,22 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -1014,28 +1014,28 @@
         <v>43221</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" t="s">
         <v>27</v>
@@ -1058,25 +1058,25 @@
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
         <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1087,13 +1087,13 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -1102,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
         <v>9</v>
@@ -1119,25 +1119,25 @@
         <v>43313</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
@@ -1160,7 +1160,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
         <v>67</v>
@@ -1210,7 +1210,7 @@
         <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" t="s">
         <v>34</v>
@@ -1236,7 +1236,7 @@
         <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
         <v>47</v>
@@ -1259,22 +1259,22 @@
         <v>43435</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
@@ -1283,7 +1283,7 @@
         <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
@@ -1294,22 +1294,22 @@
         <v>43466</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
         <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" t="n">
-        <v>12</v>
       </c>
       <c r="H21" t="s">
         <v>21</v>
@@ -1344,16 +1344,16 @@
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I22" t="n">
         <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
         <v>8</v>
@@ -1367,7 +1367,7 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
         <v>19</v>
@@ -1402,13 +1402,13 @@
         <v>18</v>
       </c>
       <c r="C24" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
@@ -1423,10 +1423,10 @@
         <v>5</v>
       </c>
       <c r="J24" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1434,13 +1434,13 @@
         <v>43586</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" t="n">
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
         <v>43</v>
@@ -1449,16 +1449,16 @@
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
@@ -1472,7 +1472,7 @@
         <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
@@ -1481,19 +1481,19 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G26" t="n">
         <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I26" t="n">
         <v>7</v>
       </c>
       <c r="J26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
@@ -1507,31 +1507,31 @@
         <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
         <v>14</v>
       </c>
       <c r="F27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="s">
         <v>44</v>
       </c>
-      <c r="G27" t="n">
-        <v>11</v>
-      </c>
-      <c r="H27" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" t="s">
-        <v>16</v>
-      </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1545,28 +1545,28 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
       </c>
       <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" t="s">
         <v>18</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9</v>
-      </c>
-      <c r="H28" t="s">
-        <v>26</v>
       </c>
       <c r="I28" t="n">
         <v>9</v>
       </c>
       <c r="J28" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1574,28 +1574,28 @@
         <v>43709</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
         <v>8</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J29" t="s">
         <v>37</v>
@@ -1612,7 +1612,7 @@
         <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="s">
         <v>19</v>
@@ -1621,22 +1621,22 @@
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I30" t="n">
         <v>5</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1647,7 +1647,7 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -1668,7 +1668,7 @@
         <v>53</v>
       </c>
       <c r="J31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
         <v>9</v>
@@ -1679,34 +1679,34 @@
         <v>43800</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
         <v>25</v>
       </c>
-      <c r="G32" t="n">
-        <v>8</v>
-      </c>
-      <c r="H32" t="s">
-        <v>26</v>
-      </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J32" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1717,10 +1717,10 @@
         <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
         <v>4</v>
@@ -1752,13 +1752,13 @@
         <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
         <v>29</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="J34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K34" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
         <v>43891</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
         <v>6</v>
@@ -1796,7 +1796,7 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
         <v>5</v>
@@ -1805,13 +1805,13 @@
         <v>11</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" t="s">
         <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1819,19 +1819,19 @@
         <v>43922</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="n">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E36" t="n">
         <v>30</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" t="n">
         <v>11</v>
@@ -1854,19 +1854,19 @@
         <v>43952</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C37" t="n">
         <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E37" t="n">
         <v>107</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" t="n">
         <v>19</v>
@@ -1878,7 +1878,7 @@
         <v>15</v>
       </c>
       <c r="J37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
         <v>14</v>
@@ -1907,13 +1907,13 @@
         <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I38" t="n">
         <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
         <v>12</v>
@@ -1936,19 +1936,19 @@
         <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G39" t="n">
         <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I39" t="n">
         <v>34</v>
       </c>
       <c r="J39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K39" t="n">
         <v>17</v>
@@ -1965,13 +1965,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E40" t="n">
         <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
         <v>9</v>
@@ -2000,7 +2000,7 @@
         <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E41" t="n">
         <v>9</v>
@@ -2018,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="J41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
@@ -2029,13 +2029,13 @@
         <v>44105</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C42" t="n">
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E42" t="n">
         <v>44</v>
@@ -2047,13 +2047,13 @@
         <v>28</v>
       </c>
       <c r="H42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I42" t="n">
         <v>14</v>
       </c>
       <c r="J42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
         <v>12</v>
@@ -2064,7 +2064,7 @@
         <v>44136</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
         <v>11</v>
@@ -2082,13 +2082,13 @@
         <v>6</v>
       </c>
       <c r="H43" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="I43" t="n">
         <v>5</v>
       </c>
       <c r="J43" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K43" t="n">
         <v>5</v>
@@ -2105,13 +2105,13 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" t="n">
         <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G44" t="n">
         <v>7</v>
@@ -2140,7 +2140,7 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E45" t="n">
         <v>17</v>
@@ -2158,7 +2158,7 @@
         <v>11</v>
       </c>
       <c r="J45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K45" t="n">
         <v>9</v>
@@ -2175,25 +2175,25 @@
         <v>37</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E46" t="n">
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G46" t="n">
         <v>13</v>
       </c>
       <c r="H46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I46" t="n">
         <v>13</v>
       </c>
       <c r="J46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K46" t="n">
         <v>12</v>
@@ -2204,13 +2204,13 @@
         <v>44256</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" t="n">
         <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
         <v>61</v>
@@ -2222,7 +2222,7 @@
         <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I47" t="n">
         <v>15</v>
@@ -2239,13 +2239,13 @@
         <v>44287</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" t="n">
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E48" t="n">
         <v>10</v>
@@ -2292,13 +2292,13 @@
         <v>56</v>
       </c>
       <c r="H49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I49" t="n">
         <v>56</v>
       </c>
       <c r="J49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
         <v>55</v>
@@ -2315,7 +2315,7 @@
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E50" t="n">
         <v>20</v>
@@ -2333,7 +2333,7 @@
         <v>14</v>
       </c>
       <c r="J50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K50" t="n">
         <v>13</v>
@@ -2350,13 +2350,13 @@
         <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
         <v>20</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G51" t="n">
         <v>18</v>
@@ -2368,7 +2368,7 @@
         <v>17</v>
       </c>
       <c r="J51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
         <v>11</v>
@@ -2379,7 +2379,7 @@
         <v>44409</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C52" t="n">
         <v>92</v>
@@ -2391,7 +2391,7 @@
         <v>88</v>
       </c>
       <c r="F52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G52" t="n">
         <v>10</v>
@@ -2414,7 +2414,7 @@
         <v>44440</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53" t="n">
         <v>11</v>
@@ -2473,7 +2473,7 @@
         <v>7</v>
       </c>
       <c r="J54" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K54" t="n">
         <v>6</v>
@@ -2490,19 +2490,19 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E55" t="n">
         <v>14</v>
       </c>
       <c r="F55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
         <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I55" t="n">
         <v>6</v>
@@ -2519,19 +2519,19 @@
         <v>44531</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" t="n">
         <v>54</v>
       </c>
       <c r="D56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G56" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
         <v>11</v>
       </c>
       <c r="H57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I57" t="n">
         <v>11</v>
@@ -2613,7 +2613,7 @@
         <v>7</v>
       </c>
       <c r="J58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K58" t="n">
         <v>6</v>
@@ -2659,13 +2659,13 @@
         <v>44652</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C60" t="n">
         <v>7</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E60" t="n">
         <v>4</v>
@@ -2677,7 +2677,7 @@
         <v>3</v>
       </c>
       <c r="H60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I60" t="n">
         <v>2</v>
@@ -2725,19 +2725,19 @@
         <v>15</v>
       </c>
       <c r="F62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G62" t="n">
         <v>12</v>
       </c>
       <c r="H62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I62" t="n">
         <v>12</v>
       </c>
       <c r="J62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K62" t="n">
         <v>12</v>
@@ -2772,7 +2772,7 @@
         <v>12</v>
       </c>
       <c r="J63" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
         <v>10</v>
@@ -2786,13 +2786,13 @@
         <v>12</v>
       </c>
       <c r="C64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
@@ -2801,13 +2801,13 @@
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I64" t="n">
         <v>11</v>
       </c>
       <c r="J64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K64" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -2830,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G65" t="n">
         <v>8</v>
@@ -2865,19 +2865,19 @@
         <v>56</v>
       </c>
       <c r="F66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
         <v>56</v>
       </c>
       <c r="H66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I66" t="n">
         <v>55</v>
       </c>
       <c r="J66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K66" t="n">
         <v>53</v>
@@ -2947,7 +2947,7 @@
         <v>6</v>
       </c>
       <c r="J68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K68" t="n">
         <v>5</v>
@@ -2970,7 +2970,7 @@
         <v>63</v>
       </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G69" t="n">
         <v>62</v>
@@ -3052,7 +3052,7 @@
         <v>14</v>
       </c>
       <c r="J71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K71" t="n">
         <v>11</v>
@@ -3069,13 +3069,13 @@
         <v>27</v>
       </c>
       <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11</v>
+      </c>
+      <c r="F72" t="s">
         <v>25</v>
-      </c>
-      <c r="E72" t="n">
-        <v>11</v>
-      </c>
-      <c r="F72" t="s">
-        <v>26</v>
       </c>
       <c r="G72" t="n">
         <v>11</v>
@@ -3122,7 +3122,7 @@
         <v>17</v>
       </c>
       <c r="J73" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K73" t="n">
         <v>12</v>
@@ -3145,16 +3145,16 @@
         <v>15</v>
       </c>
       <c r="F74" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="G74" t="n">
         <v>13</v>
       </c>
       <c r="H74" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="I74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
@@ -3186,7 +3186,7 @@
         <v>17</v>
       </c>
       <c r="H75" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I75" t="n">
         <v>17</v>
@@ -3221,13 +3221,13 @@
         <v>35</v>
       </c>
       <c r="H76" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I76" t="n">
         <v>27</v>
       </c>
       <c r="J76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K76" t="n">
         <v>17</v>
@@ -3250,13 +3250,13 @@
         <v>53</v>
       </c>
       <c r="F77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G77" t="n">
         <v>53</v>
       </c>
       <c r="H77" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I77" t="n">
         <v>48</v>
@@ -3279,13 +3279,13 @@
         <v>41</v>
       </c>
       <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" t="n">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
         <v>70</v>
-      </c>
-      <c r="E78" t="n">
-        <v>12</v>
-      </c>
-      <c r="F78" t="s">
-        <v>71</v>
       </c>
       <c r="G78" t="n">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="J78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K78" t="n">
         <v>6</v>
@@ -3314,13 +3314,13 @@
         <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E79" t="n">
         <v>33</v>
       </c>
       <c r="F79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G79" t="n">
         <v>33</v>
@@ -3332,7 +3332,7 @@
         <v>24</v>
       </c>
       <c r="J79" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K79" t="n">
         <v>14</v>
@@ -3343,13 +3343,13 @@
         <v>45261</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C80" t="n">
         <v>36</v>
       </c>
       <c r="D80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E80" t="n">
         <v>34</v>
@@ -3384,7 +3384,7 @@
         <v>61</v>
       </c>
       <c r="D81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E81" t="n">
         <v>53</v>
@@ -3402,7 +3402,7 @@
         <v>15</v>
       </c>
       <c r="J81" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K81" t="n">
         <v>8</v>
@@ -3425,22 +3425,22 @@
         <v>19</v>
       </c>
       <c r="F82" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" t="n">
+        <v>11</v>
+      </c>
+      <c r="H82" t="s">
         <v>26</v>
-      </c>
-      <c r="G82" t="n">
-        <v>11</v>
-      </c>
-      <c r="H82" t="s">
-        <v>25</v>
       </c>
       <c r="I82" t="n">
         <v>7</v>
       </c>
       <c r="J82" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -3466,13 +3466,13 @@
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I83" t="n">
         <v>8</v>
       </c>
       <c r="J83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K83" t="n">
         <v>7</v>
@@ -3507,7 +3507,7 @@
         <v>25</v>
       </c>
       <c r="J84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K84" t="n">
         <v>10</v>
@@ -3530,7 +3530,7 @@
         <v>14</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G85" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K85" t="n">
         <v>9</v>
@@ -3565,7 +3565,7 @@
         <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G86" t="n">
         <v>16</v>
@@ -3577,7 +3577,7 @@
         <v>13</v>
       </c>
       <c r="J86" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K86" t="n">
         <v>7</v>
@@ -3600,7 +3600,7 @@
         <v>22</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G87" t="n">
         <v>22</v>
@@ -3612,7 +3612,7 @@
         <v>15</v>
       </c>
       <c r="J87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K87" t="n">
         <v>14</v>
@@ -3647,7 +3647,7 @@
         <v>8</v>
       </c>
       <c r="J88" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K88" t="n">
         <v>7</v>
@@ -3658,7 +3658,7 @@
         <v>45536</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C89" t="n">
         <v>64</v>
@@ -3670,13 +3670,13 @@
         <v>44</v>
       </c>
       <c r="F89" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G89" t="n">
         <v>40</v>
       </c>
       <c r="H89" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I89" t="n">
         <v>27</v>
@@ -3711,13 +3711,13 @@
         <v>13</v>
       </c>
       <c r="H90" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" t="n">
+        <v>12</v>
+      </c>
+      <c r="J90" t="s">
         <v>26</v>
-      </c>
-      <c r="I90" t="n">
-        <v>12</v>
-      </c>
-      <c r="J90" t="s">
-        <v>25</v>
       </c>
       <c r="K90" t="n">
         <v>11</v>
@@ -3752,7 +3752,7 @@
         <v>6</v>
       </c>
       <c r="J91" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K91" t="n">
         <v>6</v>
@@ -3769,7 +3769,7 @@
         <v>40</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E92" t="n">
         <v>20</v>
@@ -3822,7 +3822,7 @@
         <v>6</v>
       </c>
       <c r="J93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K93" t="n">
         <v>6</v>
@@ -3839,7 +3839,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E94" t="n">
         <v>12</v>
@@ -3857,7 +3857,7 @@
         <v>10</v>
       </c>
       <c r="J94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K94" t="n">
         <v>10</v>
@@ -3886,13 +3886,13 @@
         <v>11</v>
       </c>
       <c r="H95" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I95" t="n">
         <v>9</v>
       </c>
       <c r="J95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K95" t="n">
         <v>8</v>
@@ -3903,7 +3903,7 @@
         <v>45748</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C96" t="n">
         <v>56</v>
@@ -3915,13 +3915,13 @@
         <v>55</v>
       </c>
       <c r="F96" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G96" t="n">
         <v>54</v>
       </c>
       <c r="H96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I96" t="n">
         <v>53</v>
@@ -3947,7 +3947,7 @@
         <v>16</v>
       </c>
       <c r="E97" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F97" t="s">
         <v>17</v>
@@ -3956,7 +3956,7 @@
         <v>14</v>
       </c>
       <c r="H97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I97" t="n">
         <v>7</v>
@@ -3979,7 +3979,7 @@
         <v>63</v>
       </c>
       <c r="D98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E98" t="n">
         <v>53</v>
@@ -3991,16 +3991,16 @@
         <v>44</v>
       </c>
       <c r="H98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J98" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
@@ -4032,7 +4032,7 @@
         <v>31</v>
       </c>
       <c r="J99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K99" t="n">
         <v>21</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="F100" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G100" t="n">
         <v>26</v>
@@ -4090,13 +4090,13 @@
         <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G101" t="n">
         <v>14</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I101" t="n">
         <v>12</v>
@@ -4119,7 +4119,7 @@
         <v>36</v>
       </c>
       <c r="D102" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E102" t="n">
         <v>13</v>
@@ -4131,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="H102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I102" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
         <v>45962</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C103" t="n">
         <v>60</v>
@@ -4166,13 +4166,13 @@
         <v>9</v>
       </c>
       <c r="H103" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I103" t="n">
         <v>9</v>
       </c>
       <c r="J103" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K103" t="n">
         <v>8</v>
@@ -4189,25 +4189,25 @@
         <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G104" t="n">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I104" t="n">
         <v>8</v>
       </c>
       <c r="J104" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K104" t="n">
         <v>6</v>
@@ -4224,7 +4224,7 @@
         <v>57</v>
       </c>
       <c r="D105" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E105" t="n">
         <v>33</v>
@@ -4242,7 +4242,7 @@
         <v>11</v>
       </c>
       <c r="J105" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K105" t="n">
         <v>11</v>
@@ -4271,13 +4271,13 @@
         <v>19</v>
       </c>
       <c r="H106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I106" t="n">
         <v>12</v>
       </c>
       <c r="J106" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K106" t="n">
         <v>11</v>
@@ -4291,7 +4291,7 @@
         <v>12</v>
       </c>
       <c r="C107" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D107" t="s">
         <v>17</v>
@@ -4306,16 +4306,16 @@
         <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I107" t="n">
         <v>9</v>
       </c>
       <c r="J107" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="K107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4552,13 +4552,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{696B2AA3-1754-461A-813B-8F134981427B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD938C5-50A8-4387-BF41-AFEED0C13DD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C1C177-C301-40E2-909E-FB1CCA487DF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EC6FF08-D427-4D4A-8C29-5AAE2E0C7A60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F8320EB-54AA-4679-8A72-2C8C478A65DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB18B73-352F-4E40-99CE-BEDCC4019846}"/>
 </file>
--- a/data/ALLE_topthemen_zeitreihe.xlsx
+++ b/data/ALLE_topthemen_zeitreihe.xlsx
@@ -4552,13 +4552,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD938C5-50A8-4387-BF41-AFEED0C13DD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B099734D-A2FF-463E-BC1C-C11F09BAE7F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EC6FF08-D427-4D4A-8C29-5AAE2E0C7A60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDBE062F-A541-449A-A3EC-817FA8C098AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB18B73-352F-4E40-99CE-BEDCC4019846}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C21C2F0-04DC-4E1D-9D82-1CC86265B719}"/>
 </file>